--- a/기획/머니첵_계산기_기획.xlsx
+++ b/기획/머니첵_계산기_기획.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'도구목록'!$A$1:$Q$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'도구목록'!$A$1:$R$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -78,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -88,6 +94,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,26 +460,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,82 +492,92 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>갱신월 · 참고</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>머니첵 분류</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>대기열 분류</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>제도</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>도구 제목(검색어 그대로)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>종류</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>각도</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>입력값</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>출력값</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>산식 근거(기관·자료)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>공식 도구 유무</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>경쟁도(감)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>예상 수요(감)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>대기열 관련 제목 수</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>연 갱신 값</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>우선순위(1먼저)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>사용</t>
         </is>
       </c>
     </row>
@@ -568,78 +587,88 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1월 · 선정기준액·기준연금액 전년 12/31 고시→1/1 적용, 사업안내 1월 게시 (확인). 개인자료는 4월 이자소득·상반기 공시가격 반영</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>기초연금</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>기초연금 계산기 (소득인정액·감액 후 월 수령액)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>나이·소득·재산·부채·배우자 유무</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>소득인정액, 선정 여부, 월 수령액</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>보건복지부 기초연금 선정기준액·소득인정액 산식</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>공단 모의계산(깊이 숨음)</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>선정기준액·기준연금액(매년 1월)</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>모든 노인 도구의 뿌리</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
         </is>
       </c>
     </row>
@@ -649,76 +678,81 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>1월 · 선정기준액 1/1 (확인)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>기초연금</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>기초연금 소득 얼마까지 안 깎이나 계산기</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>경계선</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>월 소득·재산</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>감액 시작 소득선, 전액 수령 상한</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>기초연금 소득역전방지 감액 산식</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="O3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>선정기준액</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -726,76 +760,81 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기준연금액·국민연금 A급여액 물가연동 1/1 (확인)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>기초연금</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>국민연금 받으면 기초연금 얼마 깎이나 계산기</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>국민연금 월액·가입기간</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>연계감액액, 최종 기초연금</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>국민연금 연계 감액 산식(A급여)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>기준연금액</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>검색 많고 답 없는 질문</t>
         </is>
@@ -807,76 +846,81 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기본재산액 고시 1/1 (확인). 주택 공시가격은 4~6월 갱신분 반영</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>기초연금</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>집 팔면 기초연금 얼마 줄어드나 계산기</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>변화</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>주택 매각액·거주지</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>재산 소득환산액 변화, 수령액 변화</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>재산의 소득환산 산식(지역별 기본공제)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>지역별 기본재산공제</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -884,76 +928,81 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>1월 · 선정기준액·기준연금액 1/1 (확인)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>기초연금</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>부부 vs 단독 기초연금 차이 계산기</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>부부 여부·각자 소득</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>단독 vs 부부가구 수령액(부부감액 20%)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>부부감액 규정</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>기준연금액</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -961,76 +1010,81 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>1월 · 장기요양 수가·본인부담 한도 1/1 (전년 10~11월 장기요양위원회 결정)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>장기요양보험</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>장기요양 본인부담금 계산기 (등급·재가/시설)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>등급·이용 형태·감경 대상 여부</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>월 한도액, 본인부담금</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>장기요양보험 급여비용 고시</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="O7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>월 한도액(매년)</t>
         </is>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1038,76 +1092,81 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기초급여액 물가연동·선정기준액 1/1 고시</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>장애인연금</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>장애인연금·장애수당 월 수령액 계산기</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>장애 정도·소득·재산·나이</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>기초급여+부가급여 월액</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>장애인연금 선정기준·급여액 고시</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="O8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>선정기준액</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1115,76 +1174,81 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>1월 · 보훈급여금 매년 1월 인상(예산)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>국가유공자</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>국가유공자 보훈급여 등급별 월액 조회</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>조회</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>등급·유형</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>월 보상금·수당 합계</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>국가보훈부 보상금 지급 기준표</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>없음(표만)</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>보상금 단가(매년)</t>
         </is>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1192,76 +1256,81 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기준중위소득 전년 7~8월 결정→1/1 적용, 생계급여 선정기준 32%</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>기초생활보장</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>생계급여 얼마 받나 계산기</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>가구원·소득인정액</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>선정기준, 지급액(기준−소득)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>생계급여 선정기준(중위소득 32%)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="O10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>중위소득(매년)</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1269,76 +1338,81 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기준중위소득 1/1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>기초생활보장</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>기초생활 수급 탈락선 계산기 (소득 얼마 넘으면)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>경계선</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>가구원·소득·재산</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>급여별 탈락 소득선</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>급여별 선정기준 %</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="O11" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>중위소득</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="Q11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1346,76 +1420,81 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>1월 · 긴급복지 생계지원 금액 1월 고시(중위소득 연동)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>긴급복지</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>긴급복지 생계지원 대상·금액 판정기</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>위기 사유·가구원·소득·재산</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>대상 여부, 지원 금액·기간</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>긴급복지지원법 기준(중위소득 75%)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="O12" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>기준액(매년)</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1423,76 +1502,81 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>1월 · 예산·시행령 1/1 (금액 변동 없는 해 많음)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>부모급여·아동수당</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>부모급여·아동수당·양육수당 합산 계산기</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>자녀 나이·수·어린이집 이용 여부</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>월 합계, 연 합계</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>복지부 부모급여·아동수당 지급 기준</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>없음(제도별 표만)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="O13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>지급액(매년)</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="Q13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>출산 가구 필수 검색</t>
         </is>
@@ -1504,76 +1588,81 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>1월 · 지자체 조례·예산 연초, 연중 수시 변동 (감)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>출산지원금</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>우리 지역 출산지원금 총액 계산기 (국가+지자체)</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>변화</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>거주 시군구·출생 순위</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>첫만남이용권+지자체 출산장려금 합계</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>지자체별 출산지원금 조례(수집 필요)</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="O14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>지자체 금액(수시)</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>지역 데이터 수집이 관건</t>
         </is>
@@ -1585,76 +1674,81 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>1월 · 중위소득·지원단가 1/1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>한부모가족</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>한부모 아동양육비 얼마 받나 판정기</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>소득·자녀 나이·수</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>대상 여부, 월 양육비</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>한부모가족지원법 선정기준(중위소득 63%)</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="O15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>중위소득</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="Q15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1662,76 +1756,81 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>수시 · 제도별 상이, 연초 위주 (감)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>다자녀</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>다자녀 혜택 합계 계산기 (3자녀면 뭐가 얼마)</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>자녀 수·지역</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>혜택 목록·합계</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>제도별 다자녀 기준(2자녀 확대 반영)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>제도별 기준</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="Q16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1739,78 +1838,88 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>1월 · 상한액 고용부 고시·하한액 최저임금 연동 1/1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>실업급여</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>실업급여 계산기 (일액·지급일수·총액)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>나이·가입기간·퇴직 전 3개월 임금</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>구직급여일액, 소정급여일수, 총액</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>고용보험법 구직급여 산식(평균임금 60%, 상·하한)</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>고용보험 모의계산(불친절)</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="O17" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>상한액·하한액(매년)</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>검색 최대급</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위, 버는 돈 몫)</t>
         </is>
       </c>
     </row>
@@ -1820,76 +1929,81 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>1월 · 16번과 동일</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>실업급여</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>실업급여 퇴사일 언제가 유리한가 계산기</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>시기</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>입사일·예정 퇴사일·임금</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>가입기간 구간 경계, 유리한 퇴사일</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>소정급여일수 표(가입기간·나이)</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="O18" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>상한액</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="Q18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1897,76 +2011,81 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>1월 · 하한액·소득 공제 기준 1/1 (감)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>실업급여</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>실업급여 받으면서 알바 얼마까지 되나 판정기</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>알바 소득·근무시간</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>신고 의무, 감액·중단 여부</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>고용보험법 취업 인정 기준(주 15시간·소득)</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="O19" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>하한액</t>
         </is>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>검색 많고 답 흩어짐</t>
         </is>
@@ -1978,72 +2097,77 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>1월 · 16번과 동일</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>실업급여</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>조기재취업수당 vs 끝까지 받기 손익 계산기</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>손해</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>남은 급여일수·재취업 시점</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>조기재취업수당액 vs 잔여 급여 총액</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>조기재취업수당 산식(잔여 1/2)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="O20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="n">
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2051,76 +2175,81 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>1월 · 건보료율 1/1, 지역가입자 부과자료 11월 갱신</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>실업급여</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>실업급여 받으면 건강보험료 얼마 오르나 계산기</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>뒤탈</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>퇴직 전 직장보험료·재산</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>지역가입 전환 시 보험료, 임의계속가입 비교</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>건보 지역가입자 산정 기준·임의계속가입</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="O21" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>보험료율(매년)</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n">
+      <c r="Q21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2128,76 +2257,81 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>1월 · 구직촉진수당·소득기준(중위소득) 1/1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>국민취업지원제도</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>국민취업지원제도 구직촉진수당 대상·금액 판정기</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>나이·소득·재산·취업경험</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>유형(1·2), 수당 월액·기간</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>요건(중위소득 60%·재산 4억)</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="O22" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>중위소득</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="Q22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2205,76 +2339,81 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>1월 · 고용보험법 시행령 개정 통상 1/1 (2025 개편)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>육아휴직급여</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>육아휴직급여 계산기 (2025 개편 반영)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>통상임금·휴직 개월·부부 동시 여부</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>월 급여액, 총액, 6+6 특례</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>고용보험법 육아휴직급여 상한</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>고용보험 계산기(불편)</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="O23" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>상한액(매년)</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2282,76 +2421,81 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>1월 · 상한액 고시 1/1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>출산전후휴가</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>출산휴가급여 계산기 (회사 vs 고용보험 몫)</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>통상임금·기업 규모</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>90일 급여, 고용보험 지급분</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>출산전후휴가급여 상한</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="O24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>상한액</t>
         </is>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="Q24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2359,76 +2503,81 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>1월 · 최고·최저 보상기준금액 고용부 고시 1/1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>산재보험</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>산재 휴업급여·장해급여 계산기</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>평균임금·휴업일수·장해등급</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>휴업급여(70%), 장해급여</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>산재보험법 급여 산식</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="O25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>최저·최고 보상기준</t>
         </is>
       </c>
-      <c r="P25" s="2" t="n">
+      <c r="Q25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -2436,76 +2585,86 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 개정 1/1 시행(전년 7월 개정안→12월 국회). 정기신청 5월·반기 9월</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>근로장려금</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>근로장려금·자녀장려금 계산기</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>가구 유형·근로소득·재산</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>장려금 예상액</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>국세청 근로장려금 산정표</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>국세청 계산기(홈택스 로그인)</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="O26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>산정표(매년)</t>
         </is>
       </c>
-      <c r="P26" s="2" t="n">
+      <c r="Q26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -2513,76 +2672,81 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>1월 · 25번과 동일</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>근로장려금</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>근로장려금 탈락선 계산기 (소득·재산 얼마 넘으면)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>경계선</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>가구 유형·소득·재산</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>지급 상한 소득, 재산 2억 감액 여부</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>근로장려금 요건</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="O27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>기준(매년)</t>
         </is>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="Q27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -2590,76 +2754,81 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1, 연말정산 1~2월</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>월세 세액공제</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>월세 세액공제 환급액 계산기</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>총급여·월세·주택 규모</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>공제율(15/17%), 환급액</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>조세특례제한법 월세세액공제</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>없음(설명글만)</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>한도·공제율</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="Q28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>연말정산 시즌 폭발</t>
         </is>
@@ -2671,76 +2840,81 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>청약 소득공제</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>청약통장 소득공제 실제 감세액 계산기</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>연 납입액·과세표준 구간</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>공제액, 실제 세금 감소분(지방세 포함)</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>주택청약종합저축 소득공제(연 300만·40%)</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="O29" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>한도</t>
         </is>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="Q29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>시험 글 A에서 검증됨</t>
         </is>
@@ -2752,76 +2926,81 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1, 간소화 1/15 오픈</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>연말정산</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>연말정산 환급 예상 계산기 (간이)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>총급여·부양가족·주요 공제</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>결정세액, 예상 환급/추가납부</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>소득세법 세율·공제표</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>국세청·삼쩜삼 점유</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="O30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>세율표(매년)</t>
         </is>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>경쟁 큼, 후순위</t>
         </is>
@@ -2833,76 +3012,81 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>1월 · 29번과 동일</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>연말정산</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>맞벌이 부양가족 누가 올려야 유리한가 계산기</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>부부 각 급여·공제 항목</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>배분별 세액 비교</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>소득세 누진세율</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="O31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>세율표</t>
         </is>
       </c>
-      <c r="P31" s="2" t="n">
+      <c r="Q31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -2910,76 +3094,81 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>수시 · 환급률·대상 변경 공고 시 (2025.1 다자녀 등) (감)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>교통비 환급</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>K-패스 교통비 환급액 계산기</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>월 이용 횟수·요금·유형(청년·저소득)</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>월 환급액, 연 환급액</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>K-패스 환급률(20/30/53%)</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="O32" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>환급률</t>
         </is>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="Q32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2987,76 +3176,81 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>1월 · 상한액 매년 1월 고시(물가연동), 사후환급 8월</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>국민건강보험</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>본인부담상한액 계산기 (건보 환급 예상)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>소득분위·연간 본인부담액</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>상한액, 환급 예상액</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>본인부담상한제 소득분위별 상한액</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>공단 조회(로그인)</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="O33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>상한액(매년)</t>
         </is>
       </c>
-      <c r="P33" s="2" t="n">
+      <c r="Q33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3064,76 +3258,81 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1, 신고 5월</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>돌려받는 돈</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>국세 환급</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>종합소득세 환급 예상 계산기 (프리랜서 3.3%)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>연 수입·경비율·기납부세액</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>결정세액, 환급액</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>단순경비율·세율표</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>삼쩜삼 등 점유</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>경비율(매년)</t>
         </is>
       </c>
-      <c r="P34" s="2" t="n">
+      <c r="Q34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>경쟁 큼</t>
         </is>
@@ -3145,76 +3344,86 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>수시 · 서민금융진흥원 금리·한도 연초·하반기 조정 (감)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>햇살론</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>햇살론 자격·한도 판정기 (유스·15·뱅크)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>나이·소득·신용점수·재직</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>가능 상품, 한도, 금리 범위</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>서민금융진흥원 상품별 요건</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>없음(상품 설명만)</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="O35" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>요건(수시)</t>
         </is>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="Q35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -3222,72 +3431,77 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>수시 · 34번과 동일 (감)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>햇살론</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>햇살론 월 상환액·총이자 계산기</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>대출액·기간·금리·상환방식</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>월 상환액, 총이자</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>원리금균등 산식</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>일반 대출계산기 있음</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="O36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="n">
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -3295,76 +3509,81 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>수시 · 공고 기반 (감)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>소액생계비대출</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>소액생계비대출 자격·이자 계산기</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>신용점수·소득·연체 여부</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>가능 여부, 한도, 이자·금리인하</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>서민금융진흥원 요건</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="O37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>금리(수시)</t>
         </is>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="Q37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -3372,76 +3591,81 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
+          <t>1월·7월 · 학기별 대출금리 교육부 고시</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>학자금대출</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>학자금대출 이자·상환액 계산기 (취업 후 상환)</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>대출액·금리·상환 방식·연소득</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>월 상환액, 총이자, 의무상환 개시</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
         <is>
           <t>한국장학재단 상환 기준</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>재단 계산기 있음</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="O38" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>금리·상환기준소득(매년)</t>
         </is>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="Q38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -3449,76 +3673,81 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>수시 · 지자체 공고(연초 위주) (감)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>학자금대출</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>학자금대출 이자 지원 얼마 받나 판정기 (지자체)</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>거주지·소득·대출 종류</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>지자체 이자지원 대상, 지원액</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>지자체별 이자지원 조례</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="O39" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="O39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>지자체 기준</t>
         </is>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="Q39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>대기열에 직결</t>
         </is>
@@ -3530,76 +3759,81 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
+          <t>수시 · 국토부 기금대출 금리 수시 조정 (감)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>전세대출</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>전세보증금 대출 한도 계산기 (버팀목·청년)</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>보증금·소득·나이·무주택</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>가능 상품, 한도, 금리</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>주택도시기금 상품별 요건</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>기금 안내(계산기 없음)</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="O40" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>한도·금리(수시)</t>
         </is>
       </c>
-      <c r="P40" s="2" t="n">
+      <c r="Q40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -3607,76 +3841,81 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
+          <t>수시 · 금융위 규제(7월 스트레스DSR 단계 등) (감)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>주택담보대출</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>DSR·LTV 대출 한도 계산기</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>연소득·기존 대출·주택가·지역</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>DSR 40% 한도, LTV 한도</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
         <is>
           <t>금융위 DSR·LTV 규제</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>은행 계산기 다수</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="O41" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>규제(수시)</t>
         </is>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="Q41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>경쟁 큼</t>
         </is>
@@ -3688,76 +3927,81 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>1월 · 중기부 창업지원 통합공고 1월 초</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>창업지원</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>창업 지원금 한눈에 판정기 (예비·초기·청년)</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>업력·나이·업종·지역</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>해당 사업 목록, 지원 한도</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>중기부·지자체 창업사업 요건</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="O42" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>공고(수시)</t>
         </is>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="Q42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -3765,72 +4009,77 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
+          <t>수시 · 신복위 기준 변경 시 (감)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
           <t>빌리는 돈</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>신용회복</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>채무조정 감면율·월 상환액 계산기 (신복위)</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>채무액·소득·연체 기간</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>감면 후 원금, 월 상환액</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>신용회복위원회 채무조정 기준</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="O43" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="n">
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3838,76 +4087,86 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기준임대료 전년 8월 고시→1/1 적용</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>주거급여</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>주거급여 계산기 (지역·가구·월세)</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>가구원·소득인정액·지역·실제 월세</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>기준임대료, 지급액</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>주거급여 기준임대료(급지·가구별)</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="O44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>기준임대료(매년)</t>
         </is>
       </c>
-      <c r="P44" s="2" t="n">
+      <c r="Q44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -3915,76 +4174,81 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
+          <t>1월 · 43번과 동일</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>주거급여</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>이사하면 주거급여 얼마 바뀌나 계산기</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>변화</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>현 지역·새 지역·월세</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>급지 변화에 따른 지급액 차이</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>기준임대료 급지표</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="O45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>기준임대료</t>
         </is>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="Q45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -3992,76 +4256,81 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
+          <t>수시 · 공고 기반, 지자체 연초 (감)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>청년 월세 지원</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>청년 월세 지원 자격·금액 판정기 (국가+경기·서울)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>나이·소득·거주지·보증금·월세</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>대상 여부, 월 지원액, 기간</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>국토부 청년월세 지원 + 지자체 사업 요건</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="O46" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>기준(수시)</t>
         </is>
       </c>
-      <c r="P46" s="2" t="n">
+      <c r="Q46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>대기열에 직결</t>
         </is>
@@ -4073,72 +4342,77 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
+          <t>1월 · 주거급여 1/1, 청년월세 공고 시 (감)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>청년 월세 지원</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>주거급여 vs 청년월세 뭐가 더 받나 비교기</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>조건 공통 입력</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>두 제도 예상액·중복 가능 여부</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>양 제도 요건·중복 규정</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="O47" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="n">
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -4146,72 +4420,77 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>수시 · 주택공급규칙 개정 시, 드묾</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>청약</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>청약 가점 계산기</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>무주택 기간·부양가족·납입 기간</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>가점(84점 만점)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>청약 가점제 산정 기준</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>청약홈·은행 있음</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="O48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" s="2" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>경쟁 큼</t>
         </is>
@@ -4223,76 +4502,81 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
+          <t>수시 · 47번과 동일</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>청약</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>청년·신혼·생애최초 특별공급 자격 판정기</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>나이·혼인·소득·자산·청약통장</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>해당 특공 유형, 소득 구간</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>주택공급규칙 특공 요건</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>없음(설명글)</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="O49" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>소득 기준(매년)</t>
         </is>
       </c>
-      <c r="P49" s="2" t="n">
+      <c r="Q49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -4300,76 +4584,81 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>수시 · 규칙 개정 시(2024.11 25만원), 드묾</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>청약</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>청약통장 월 25만원 vs 10만원 인정액 계산기</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>월 납입액·기간</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>인정 납입액, 공공분양 순위 영향</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>청약통장 월 인정 한도(25만원)</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="O50" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>인정 한도</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="Q50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -4377,76 +4666,81 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
+          <t>수시 · 기준금리 결정(연 8회) 연동</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>전세</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>전세 vs 월세 어느 쪽이 싼가 계산기 (전월세 전환율)</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>보증금·월세·대출금리</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>연 비용 비교, 전환율</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>전월세전환율 법정 상한</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>계산기 다수</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="O51" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>기준금리</t>
         </is>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="Q51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -4454,76 +4748,81 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>수시 · HUG 보증료율 개정 시 (감)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>전세</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>전세보증금 반환보증 보증료 계산기</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>보증금·주택 유형·보증 기간</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>보증료, 청년·저소득 할인</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>HUG 보증료율</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>HUG 있음</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="O52" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>보증료율</t>
         </is>
       </c>
-      <c r="P52" s="2" t="n">
+      <c r="Q52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -4531,76 +4830,81 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
+          <t>1월 · 지방세법 1/1, 감면 일몰 연말 확인</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>주택 세금</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>취득세 계산기 (생애최초 감면 포함)</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>주택가·주택 수·생애최초 여부</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>취득세, 감면액</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>지방세법 취득세율·감면</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>위택스 있음</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="O53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>세율</t>
         </is>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="Q53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -4608,76 +4912,81 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>수시 · 조례 개정 시, 드묾(2021.10)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>중개수수료</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>부동산 중개수수료 계산기 (상한 요율)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>거래 유형·금액·지역</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>법정 상한 수수료</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>공인중개사법 요율표</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>계산기 다수</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="O54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>요율표</t>
         </is>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="Q54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -4685,76 +4994,81 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
+          <t>2~3월 · 전년 도시근로자 월평균소득 발표 후 공고부터 (감)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
           <t>사는 집 돈</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>주거·부동산</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>공공임대</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>행복주택·국민임대 자격 판정기</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>나이·소득·자산·차량</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>해당 유형, 소득 %</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>LH 공공임대 입주자격</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>없음(공고문)</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
+      <c r="O55" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>기준(매년)</t>
         </is>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="Q55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -4762,78 +5076,88 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
+          <t>1월 · 중위소득 연동 1/1, 개별 감면은 수시</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>요금감면</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>요금감면 합계 판정기 (수급·차상위·장애인)</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>수급 유형·가구·사용량</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>전기·가스·통신·수도·TV수신료 감면액 합계</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>각 기관 감면 기준</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="O56" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>감면액(수시)</t>
         </is>
       </c>
-      <c r="P56" s="2" t="n">
+      <c r="Q56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>한 번에 보여주는 곳 없음</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
         </is>
       </c>
     </row>
@@ -4843,76 +5167,81 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
+          <t>수시 · 한전 요금 개정 시, 여름(7~8월) 한도 상향 고정 (감)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>전기요금</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>전기요금 복지할인 얼마 깎이나 계산기</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>할인 유형·월 사용량</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>월 할인액(한도), 여름 한도</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>한전 복지할인 기준</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>한전 안내(계산기 없음)</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N57" s="2" t="n">
+      <c r="O57" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O57" s="2" t="inlineStr">
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>할인 한도</t>
         </is>
       </c>
-      <c r="P57" s="2" t="n">
+      <c r="Q57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -4920,76 +5249,81 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
+          <t>수시 · 과기정통부 고시 (감)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>통신비</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>통신비 감면 대상·월 감면액 계산기</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>수급 유형·요금제</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>월 감면액, 연 합계</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>과기부 통신요금 감면 기준</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="O58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>감면 기준</t>
         </is>
       </c>
-      <c r="P58" s="2" t="n">
+      <c r="Q58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -4997,76 +5331,81 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
+          <t>수시 · 지자체 예산·소진 따라 월 단위 변동</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>지역화폐</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>지역화폐 인센티브·할인 계산기 (지역별)</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>거주 시군·충전액</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>적립·할인액, 월 한도</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>지자체별 인센티브율(수집 필요)</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="O59" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="O59" s="2" t="inlineStr">
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>인센티브율(수시)</t>
         </is>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="Q59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q59" s="2" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>대기열 지역 제목 다수</t>
         </is>
@@ -5078,72 +5417,77 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
+          <t>수시 · 조례 (감)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>공영주차</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>공영주차장 요금 감면 대상 판정기</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>지역·차량·감면 사유</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>감면율, 등록 방법</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>지자체 주차장 조례</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="O60" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -5151,72 +5495,77 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
+          <t>수시 · (감)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>통행료</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>고속도로·연륙교 통행료 감면 판정기</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>차량·감면 사유·지역</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>감면율, 신청처</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>도로공사·지자체 감면 기준</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="O61" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -5224,76 +5573,81 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
+          <t>1월 · 보험료율 1/1(전년 8~9월 건정심), 부과자료 11월 갱신</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>건강보험</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>건강보험 지역가입자 보험료 계산기</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>소득·재산·자동차</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>월 보험료</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t>건보 지역가입자 산정 기준</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>공단 있음(로그인)</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="O62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>점수표(매년)</t>
         </is>
       </c>
-      <c r="P62" s="2" t="n">
+      <c r="Q62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -5301,72 +5655,77 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
+          <t>수시 · 세대별 갱신주기 상이 (감)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>요금감면·지역화폐·보험</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>보험</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>실손보험 세대별 보험료·자기부담 비교기</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>세대(1~4)·나이</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>월 보험료 차이, 자기부담률</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>금감원 실손 세대별 기준</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="O63" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="n">
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" s="2" t="inlineStr">
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>상품 추천 아님, 제도 비교만</t>
         </is>
@@ -5378,76 +5737,81 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
+          <t>1월·3월 · 보육료 단가 1월, 학년 시작 3월</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>보육</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>어린이집·유치원 부모 부담금 계산기</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>지역·기관 유형·자녀 나이</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>월 본인 부담</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>보육료·유아학비 지원 단가</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="O64" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>단가(매년)</t>
         </is>
       </c>
-      <c r="P64" s="2" t="n">
+      <c r="Q64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -5455,76 +5819,81 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>학기 · 1학기 11~12월·2학기 5~6월 신청, 소득구간 매 학기</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
           <t>아끼는 돈</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>가족·돌봄·교육</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>국가장학금</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>국가장학금 소득구간·지원액 판정기</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>가구 소득·재산·형제</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>소득 분위, 학기 지원액</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>한국장학재단 소득구간·지원 단가</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>재단 모의계산 있음</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O65" s="2" t="inlineStr">
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>구간 경계(매년)</t>
         </is>
       </c>
-      <c r="P65" s="2" t="n">
+      <c r="Q65" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -5532,76 +5901,81 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
+          <t>1월 · 최저임금 전년 8/5 고시→1/1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>최저임금</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>최저임금 월급·주휴수당 계산기</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>시급·주 근무시간</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>월 환산액, 주휴수당</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>최저임금법·주휴수당 산식</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>계산기 다수</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="O66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>시급(매년)</t>
         </is>
       </c>
-      <c r="P66" s="2" t="n">
+      <c r="Q66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="R66" s="2" t="inlineStr">
         <is>
           <t>경쟁 큼</t>
         </is>
@@ -5613,76 +5987,81 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>퇴직금</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>퇴직금·퇴직소득세 계산기</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>입사일·퇴사일·3개월 임금</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>퇴직금, 퇴직소득세</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>근로기준법 평균임금·퇴직소득세 산식</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>고용부 계산기 있음</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="O67" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="O67" s="2" t="inlineStr">
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>세율표</t>
         </is>
       </c>
-      <c r="P67" s="2" t="n">
+      <c r="Q67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -5690,76 +6069,81 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
+          <t>1월·7월 · 건보료율 1/1, 국민연금 기준소득월액 상·하한 7/1</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>4대보험</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>4대보험 근로자 부담액 계산기 (실수령액)</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>월급</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>공제액, 실수령</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
         <is>
           <t>보험료율(매년)</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>계산기 다수</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="O68" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>요율(매년)</t>
         </is>
       </c>
-      <c r="P68" s="2" t="n">
+      <c r="Q68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -5767,76 +6151,81 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t>1월 · 사업 1월 시작, 모집 전년 12월</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>노인일자리</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>노인일자리 사업 유형·월 수당 판정기</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>나이·소득·거주지</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>가능 유형, 월 수당</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>노인일자리 사업 지침</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N69" s="2" t="n">
+      <c r="O69" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="O69" s="2" t="inlineStr">
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>수당(매년)</t>
         </is>
       </c>
-      <c r="P69" s="2" t="n">
+      <c r="Q69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -5844,76 +6233,81 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
+          <t>1월·7월 · 지자체 상·하반기 모집</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>공공근로</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>공공근로·희망근로 자격·급여 판정기</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>나이·소득·지역</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>대상 여부, 일급·월급</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>지자체 공공근로 공고</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
+      <c r="O70" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="O70" s="2" t="inlineStr">
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>공고(반기)</t>
         </is>
       </c>
-      <c r="P70" s="2" t="n">
+      <c r="Q70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" s="2" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>대기열 지역 제목 다수</t>
         </is>
@@ -5925,76 +6319,81 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
+          <t>1월 · 훈련비 자부담률·한도 연초 (감)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>내일배움카드</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>국민내일배움카드 자부담 계산기</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>훈련 과정비·훈련 유형·취업 여부</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>정부 지원액, 본인 부담</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>내일배움카드 지원 기준</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="O71" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="O71" s="2" t="inlineStr">
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>한도</t>
         </is>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="Q71" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -6002,72 +6401,77 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
+          <t>수시 · 제도 신설·종료 잦음 (감)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>대출·서민금융·창업</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>청년 재직 공제</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>청년 재직 지원(공제·장려금) 만기 수령액 계산기</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>가입 유형·기간</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>만기 수령액(본인+기업+정부)</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>공제 유형별 적립 구조</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="O72" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="O72" s="2" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -6075,72 +6479,77 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
+          <t>연 1회 · 모집 시기 확인 필요 (감)</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
           <t>버는 돈</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>실업·고용</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>고교취업연계장려금</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>고교취업연계장려금 환수 여부·금액 판정기</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>뒤탈</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>퇴사 시점·진학 여부</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>환수 대상 여부, 환수액</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>장려금 운영 지침</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="O73" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Q73" s="2" t="inlineStr">
+      <c r="R73" s="2" t="inlineStr">
         <is>
           <t>대기열에 직결</t>
         </is>
@@ -6152,76 +6561,81 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
+          <t>수시 · 매월 가입신청, 제도 개정 시(2025.1 기여금 확대) (감)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌 만기 수령액 계산기</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>월 납입·소득 구간·가입 기간</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>정부기여금, 이자, 만기 총액</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>서민금융진흥원 기여금 매칭표</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>진흥원 계산기(단순)</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="O74" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>매칭표(수시)</t>
         </is>
       </c>
-      <c r="P74" s="2" t="n">
+      <c r="Q74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -6229,76 +6643,81 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
+          <t>수시 · 73번과 동일 (감)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌 월 40만 vs 70만 만기 차이 계산기</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>두 납입액</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>만기 차이, 기여금 효율</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
         <is>
           <t>기여금 매칭 구간</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N75" s="2" t="n">
+      <c r="O75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O75" s="2" t="inlineStr">
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>매칭표</t>
         </is>
       </c>
-      <c r="P75" s="2" t="n">
+      <c r="Q75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -6306,72 +6725,77 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
+          <t>수시 · 73번과 동일 (감)</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>청년도약계좌 중도해지 손해액 계산기 (3년 특례)</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>손해</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>가입 개월·납입액</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>해지 시 수령액, 상실분</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>중도해지 규정(3년 이상 특례)</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="O76" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -6379,76 +6803,81 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
+          <t>5월 · 매년 5월 모집</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>청년 통장</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>청년내일저축계좌 자격·만기액 판정기</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>나이·소득·재산·근로 여부</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>가입 가능, 정부지원, 만기액</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>복지부 청년내일저축계좌 요건</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="O77" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>중위소득</t>
         </is>
       </c>
-      <c r="P77" s="2" t="n">
+      <c r="Q77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -6456,76 +6885,81 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
+          <t>분기·3월 · 경기 청년기본소득 분기별, 서울 청년수당 3월 모집</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>청년수당</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>경기도 청년기본소득·서울 청년수당 대상 판정기</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>나이·거주 기간·소득</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>대상 여부, 지급액·분기</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>지자체 조례</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="O78" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>기준(매년)</t>
         </is>
       </c>
-      <c r="P78" s="2" t="n">
+      <c r="Q78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>대기열 다수</t>
         </is>
@@ -6537,76 +6971,81 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
+          <t>수시 · 상품별 공고 (감)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>적금</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>미소드림적금·희망적금류 만기 이자·지원금 계산기</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>월 납입·기간·금리·지원 유형</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>만기 이자, 정부 지원금, 총액</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>상품별 약관·지원 규정</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="O79" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="P79" s="2" t="inlineStr">
         <is>
           <t>금리(수시)</t>
         </is>
       </c>
-      <c r="P79" s="2" t="n">
+      <c r="Q79" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="R79" s="2" t="inlineStr">
         <is>
           <t>대기열에 직결</t>
         </is>
@@ -6618,76 +7057,81 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
+          <t>1월·7월 · 연금액 물가연동 1/1, 기준소득월액 상·하한 7/1</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>국민연금</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>국민연금 조기수령 vs 연기 손익분기 계산기</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>시기</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>예상 연금액·수령 나이</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>조기(−30%)·정상·연기(+36%) 누적 비교, 손익분기 나이</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>국민연금 조기·연기 감액·가산율</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>없음(공단은 예상액만)</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
+      <c r="O80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>가산율</t>
         </is>
       </c>
-      <c r="P80" s="2" t="n">
+      <c r="Q80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="R80" s="2" t="inlineStr">
         <is>
           <t>검색 큰데 도구 없음</t>
         </is>
@@ -6699,76 +7143,81 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
+          <t>1월·7월 · 79번과 동일</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>국민연금</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>국민연금 임의가입·추납하면 얼마 늘어나나 계산기</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>변화</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>추납 개월·기준소득</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>월 연금 증가액, 회수 기간</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="inlineStr">
         <is>
           <t>국민연금 급여 산식(A값·B값)</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N81" s="2" t="n">
+      <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O81" s="2" t="inlineStr">
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>A값(매년)</t>
         </is>
       </c>
-      <c r="P81" s="2" t="n">
+      <c r="Q81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -6776,72 +7225,77 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
+          <t>1월 · 연금액 물가연동 1/1</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>국민연금</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>유족연금 vs 내 노령연금 선택 계산기</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>비교</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>본인 연금·배우자 유족연금</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>중복 조정 후 수령액 비교</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>국민연금 중복급여 조정(유족연금 30%)</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="O82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="2" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -6849,76 +7303,81 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
+          <t>1월 · 세법 1/1</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>연금저축</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>연금저축·IRP 세액공제 환급액 계산기</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>납입액·총급여</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>공제율(13.2/16.5%), 환급액</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>조특법 연금계좌 세액공제 한도</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>증권사 계산기 다수</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="O83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>한도</t>
         </is>
       </c>
-      <c r="P83" s="2" t="n">
+      <c r="Q83" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -6926,72 +7385,77 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
+          <t>수시 · 규칙 개정 시</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>주택청약</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>청약통장 몇 년 부어야 1순위인가 계산기</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>시기</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>지역·가입일·납입 횟수</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>1순위 도달 시점, 필요 횟수</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>주택공급규칙 1순위 요건(지역별)</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="O84" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="O84" s="2" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -6999,78 +7463,88 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
+          <t>1월 · 기준중위소득 전년 7~8월 결정→1/1</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
           <t>모으는 돈</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>청년수당·통장</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>중위소득</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>중위소득 % 계산기 (내 가구 소득은 몇 %인가)</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>계산기</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>가구원 수·월 소득</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>중위소득 대비 %, 해당 제도 목록</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>보건복지부 기준 중위소득 고시</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>없음(표만)</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N85" s="2" t="n">
+      <c r="O85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>기준 중위소득(매년 8월 고시)</t>
         </is>
       </c>
-      <c r="P85" s="2" t="n">
+      <c r="Q85" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" s="2" t="inlineStr">
+      <c r="R85" s="2" t="inlineStr">
         <is>
           <t>모든 판정기의 입구</t>
+        </is>
+      </c>
+      <c r="S85" s="5" t="inlineStr">
+        <is>
+          <t>사용됨(1순위)</t>
         </is>
       </c>
     </row>
@@ -7080,83 +7554,88 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
+          <t>1월 · 중위소득 연동 1/1, 개별 제도 수시</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
           <t>받는 돈</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>노인·장애인·보훈 복지</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>통합</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>내가 받을 수 있는 지원금 전부 판정기 (통합)</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>판정기</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>겹침</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>나이·가구·소득·재산·지역·상황</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>해당 제도 목록 + 각 글 링크</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>위 도구들의 요건 통합</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>복지로 '복지 멤버십'(로그인·불친절)</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="O86" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>각 제도 기준</t>
         </is>
       </c>
-      <c r="P86" s="2" t="n">
+      <c r="Q86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" s="2" t="inlineStr">
+      <c r="R86" s="2" t="inlineStr">
         <is>
           <t>사이트 정체성(허브). 마지막에 만든다</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q86"/>
+  <autoFilter ref="A1:R86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
